--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.526</v>
+        <v>1.563</v>
       </c>
       <c r="D3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E3">
-        <v>0.043</v>
+        <v>0.028</v>
       </c>
       <c r="F3">
         <v>0.001</v>
       </c>
       <c r="G3">
-        <v>2.441</v>
+        <v>1.508</v>
       </c>
       <c r="H3">
-        <v>2.608</v>
+        <v>1.616</v>
       </c>
       <c r="I3">
-        <v>2.446</v>
+        <v>1.511</v>
       </c>
       <c r="J3">
-        <v>2.614</v>
+        <v>1.62</v>
       </c>
       <c r="K3">
-        <v>2.436</v>
+        <v>1.505</v>
       </c>
       <c r="L3">
-        <v>2.604</v>
+        <v>1.615</v>
       </c>
     </row>
     <row r="4">

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>2.702</v>
+        <v>1.745</v>
       </c>
       <c r="D5">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E5">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="F5">
         <v>0.001</v>
       </c>
       <c r="G5">
-        <v>2.615</v>
+        <v>1.686</v>
       </c>
       <c r="H5">
-        <v>2.79</v>
+        <v>1.803</v>
       </c>
       <c r="I5">
-        <v>2.616</v>
+        <v>1.685</v>
       </c>
       <c r="J5">
-        <v>2.791</v>
+        <v>1.805</v>
       </c>
       <c r="K5">
-        <v>2.614</v>
+        <v>1.684</v>
       </c>
       <c r="L5">
-        <v>2.789</v>
+        <v>1.805</v>
       </c>
     </row>
   </sheetData>
